--- a/mariobadescu/mariobadescu_5_upgraded_products.xlsx
+++ b/mariobadescu/mariobadescu_5_upgraded_products.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -160,6 +160,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -531,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,35 +571,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Current Word Count</t>
+          <t>Feed Word Count (Shopify API)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Live Storefront Words (Theme)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Diagnostic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Upgraded Description (Clean Readable Text + Specs)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Current Alt Text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Image Alt Text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Google Shopping Category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Smart Tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Live Product URL</t>
         </is>
@@ -622,45 +633,53 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Beauty Rest Routine | Everyday Performance &amp; Fit</t>
+          <t>Mario Badescu Beauty Rest Routine Skincare Set</t>
         </is>
       </c>
       <c r="E2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>The Beauty Rest Routine by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginMariobadescu (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F2" s="7" t="n">
+        <v>555</v>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Unlock your skin's natural glow overnight with this curated collection designed to soothe and hydrate while you sleep. Apply these essential treatments in the evening to wake up to a refreshed, deeply nourished, and visibly radiant complexion.
+Key Features &amp; Benefits
+• Overnight recovery complex to soothe stressed skin.
+• Deeply hydrating formulas for lasting moisture retention.
+• Promotes a smoother and more even skin texture by morning.
+• Formulated for all skin types including sensitive complexions.
+• Essential nighttime regimen for a healthy-looking glow.
+Includes: Nighttime treatment serums and hydrating moisture boosters. Compatibility: Safe for daily use on all skin types.</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Beauty Rest Routine - Mariobadescu Official Product View</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Mario Badescu Beauty Rest Routine skincare bundle featuring night treatment products on a white background.</t>
         </is>
       </c>
       <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care &gt; Facial Skin Care</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>Skincare Set, Night Routine, Hydration, All Skin Types, Mario Badescu, Anti-Aging</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>https://mariobadescu.com/products/beauty-rest-routine</t>
         </is>
@@ -684,45 +703,53 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Morning Brightness Routine | Everyday Performance &amp; Fit</t>
+          <t>Mario Badescu Morning Brightness Routine Skincare Kit</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>The Morning Brightness Routine by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginMariobadescu (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F3" s="7" t="n">
+        <v>595</v>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Start your day with a luminous complexion using this energizing routine tailored to brighten and revitalize tired skin. These high-performance formulas work together to defend against daily environmental stressors while providing an instant, healthy-looking glow.
+Key Features &amp; Benefits
+• Formulated to brighten dull skin and improve clarity.
+• Provides essential daytime antioxidant protection.
+• Lightweight textures absorb quickly for effortless layering.
+• Boosts skin radiance for a fresh and energized appearance.
+• Ideal for creating a smooth canvas for makeup application.
+Includes: Brightening cleanser, serum, and daytime moisturizer. Compatibility: Suitable for daily morning use for all skin types.</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Morning Brightness Routine - Mariobadescu Official Product View</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Mario Badescu Morning Brightness Routine collection featuring daily brightening skincare products on a white background.</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care &gt; Facial Skin Care</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Skincare Set, Morning Routine, Brightening, Vitamin C, All Skin Types, Daily Care</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>https://mariobadescu.com/products/morning-brightness-routine</t>
         </is>
@@ -746,45 +773,53 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Complete PDRN Routine | Everyday Performance &amp; Fit</t>
+          <t>Mario Badescu Complete PDRN Routine Skin Set</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>The Complete PDRN Routine by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginMariobadescu (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F4" s="7" t="n">
+        <v>822</v>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Transform your complexion with the regenerative power of our advanced PDRN routine designed to strengthen and revitalize skin elasticity. Use this system consistently to support a firm, youthful appearance and improve the overall resilience of your skin barrier.
+Key Features &amp; Benefits
+• Utilizes advanced PDRN technology for deep cellular support.
+• Visibly improves skin firmness and overall elasticity.
+• Helps reinforce the natural moisture barrier against damage.
+• Smoothes the appearance of fine lines and uneven texture.
+• Advanced formula suitable for all skin types and ages.
+Includes: PDRN-infused serum and restorative cream. Compatibility: Daily use for firming and anti-aging benefits.</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Complete PDRN Routine - Mariobadescu Official Product View</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Mario Badescu Complete PDRN Routine set featuring regenerative facial skincare products on a white background.</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care &gt; Facial Skin Care</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>PDRN, Anti-Aging, Firming, Skincare Routine, Mario Badescu, Skin Barrier</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>https://mariobadescu.com/products/complete-pdrn-routine</t>
         </is>
@@ -808,45 +843,53 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Salon Gift Certificates | Everyday Performance &amp; Fit</t>
+          <t>Mario Badescu Salon Physical Gift Certificate</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>The Salon Gift Certificates by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginMariobadescu (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F5" s="7" t="n">
+        <v>266</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Treat someone special to the ultimate relaxation experience with a physical gift certificate redeemable at our iconic Mario Badescu salon. This elegant gift is the perfect way to provide a loved one with world-class facial treatments and expert skincare services.
+Key Features &amp; Benefits
+• Redeemable for professional services at the Mario Badescu Salon.
+• Physical card shipped directly to your preferred address.
+• The perfect gift for any skincare enthusiast or fan.
+• High-quality presentation for a premium gifting experience.
+• Flexible usage for a variety of salon treatments.
+Type: Physical Gift Certificate. Redemption: Valid for in-salon services only.</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Salon Gift Certificates - Mariobadescu Official Product View</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Physical Mario Badescu Salon gift certificate card on a clean white background.</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Business &amp; Industrial &gt; Customer Service &gt; Gift Certificates</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Gift Card, Salon Services, Gift Ideas, Mario Badescu Salon, Physical Gift</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>https://mariobadescu.com/products/salon-gift-certificates</t>
         </is>
@@ -870,45 +913,53 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Custom Gift Certificate | Everyday Performance &amp; Fit</t>
+          <t>Mario Badescu E-Gift Certificate</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>The Custom Gift Certificate by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginMariobadescu (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F6" s="7" t="n">
+        <v>477</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Give the gift of personalized skincare with a convenient e-gift certificate that allows recipients to choose their favorite Mario Badescu products. Delivered instantly via email, this flexible option is ideal for last-minute gifting and ensures your loved one gets exactly what they need.
+Key Features &amp; Benefits
+• Delivered via email for instant, hassle-free gifting.
+• Redeemable for any product across the Mario Badescu online store.
+• Allows recipients to curate their own personalized skincare routine.
+• The perfect solution for birthdays, holidays, and special occasions.
+• No expiration dates for maximum shopping convenience.
+Type: Digital E-Gift Card. Redemption: Valid for online store purchases only.</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Custom Gift Certificate - Mariobadescu Official Product View</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Mario Badescu digital e-gift certificate card design displayed on screen.</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Business &amp; Industrial &gt; Customer Service &gt; Gift Certificates</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>E-Gift Card, Digital Gift, Skincare Gift, Online Shopping, Mario Badescu</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>https://mariobadescu.com/products/custom-gift-certificate</t>
         </is>
@@ -967,892 +1018,842 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Handle</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Body (HTML)</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Option1 Name</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Option1 Value</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Variant SKU</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Variant Grams</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Tracker</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Qty</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Policy</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>Variant Fulfillment Service</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="11" t="inlineStr">
         <is>
           <t>Variant Price</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="R1" s="11" t="inlineStr">
         <is>
           <t>Variant Compare At Price</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="S1" s="11" t="inlineStr">
         <is>
           <t>Variant Requires Shipping</t>
         </is>
       </c>
-      <c r="T1" s="10" t="inlineStr">
+      <c r="T1" s="11" t="inlineStr">
         <is>
           <t>Variant Taxable</t>
         </is>
       </c>
-      <c r="U1" s="10" t="inlineStr">
+      <c r="U1" s="11" t="inlineStr">
         <is>
           <t>Variant Barcode</t>
         </is>
       </c>
-      <c r="V1" s="10" t="inlineStr">
+      <c r="V1" s="11" t="inlineStr">
         <is>
           <t>Image Src</t>
         </is>
       </c>
-      <c r="W1" s="10" t="inlineStr">
+      <c r="W1" s="11" t="inlineStr">
         <is>
           <t>Image Position</t>
         </is>
       </c>
-      <c r="X1" s="10" t="inlineStr">
+      <c r="X1" s="11" t="inlineStr">
         <is>
           <t>Image Alt Text</t>
         </is>
       </c>
-      <c r="Y1" s="10" t="inlineStr">
+      <c r="Y1" s="11" t="inlineStr">
         <is>
           <t>Gift Card</t>
         </is>
       </c>
-      <c r="Z1" s="10" t="inlineStr">
+      <c r="Z1" s="11" t="inlineStr">
         <is>
           <t>SEO Title</t>
         </is>
       </c>
-      <c r="AA1" s="10" t="inlineStr">
+      <c r="AA1" s="11" t="inlineStr">
         <is>
           <t>SEO Description</t>
         </is>
       </c>
-      <c r="AB1" s="10" t="inlineStr">
+      <c r="AB1" s="11" t="inlineStr">
         <is>
           <t>Google Shopping / Google Product Category</t>
         </is>
       </c>
-      <c r="AC1" s="10" t="inlineStr">
+      <c r="AC1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>beauty-rest-routine</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>Beauty Rest Routine | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;Beauty Rest Routine&lt;/strong&gt; by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Mariobadescu (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu Beauty Rest Routine Skincare Set</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Unlock your skin's natural glow overnight with this curated collection designed to soothe and hydrate while you sleep. Apply these essential treatments in the evening to wake up to a refreshed, deeply nourished, and visibly radiant complexion.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Overnight recovery complex to soothe stressed skin.&lt;/li&gt;&lt;li&gt;Deeply hydrating formulas for lasting moisture retention.&lt;/li&gt;&lt;li&gt;Promotes a smoother and more even skin texture by morning.&lt;/li&gt;&lt;li&gt;Formulated for all skin types including sensitive complexions.&lt;/li&gt;&lt;li&gt;Essential nighttime regimen for a healthy-looking glow.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;Includes: Nighttime treatment serums and hydrating moisture boosters. Compatibility: Safe for daily use on all skin types.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Mariobadescu</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care &gt; Facial Skin Care</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care &gt; Facial Skin Care</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Skincare Set, Night Routine, Hydration, All Skin Types, Mario Badescu, Anti-Aging</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>BEAUTY-REST-ROUTINE-FIXED</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="O2" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr">
+      <c r="P2" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q2" s="11" t="inlineStr">
+      <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>79.00</t>
         </is>
       </c>
-      <c r="R2" s="11" t="inlineStr"/>
-      <c r="S2" s="11" t="inlineStr">
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T2" s="11" t="inlineStr">
+      <c r="T2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U2" s="11" t="inlineStr"/>
-      <c r="V2" s="11" t="inlineStr">
+      <c r="U2" s="12" t="inlineStr"/>
+      <c r="V2" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0618/8476/0291/files/1-Beauty_Rest_Bundle_OnWhite_7a6b59b9-9071-46a4-83be-f101ae5696e5.jpg?v=1792519070</t>
         </is>
       </c>
-      <c r="W2" s="11" t="inlineStr">
+      <c r="W2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X2" s="11" t="inlineStr">
-        <is>
-          <t>Beauty Rest Routine - Mariobadescu Official Product View</t>
-        </is>
-      </c>
-      <c r="Y2" s="11" t="inlineStr">
+      <c r="X2" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu Beauty Rest Routine skincare bundle featuring night treatment products on a white background.</t>
+        </is>
+      </c>
+      <c r="Y2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z2" s="11" t="inlineStr">
-        <is>
-          <t>Beauty Rest Routine | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="AA2" s="11" t="inlineStr">
-        <is>
-          <t>The  Beauty Rest Routine  by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to el</t>
-        </is>
-      </c>
-      <c r="AB2" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC2" s="11" t="inlineStr">
+      <c r="Z2" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu Beauty Rest Routine Skincare Set</t>
+        </is>
+      </c>
+      <c r="AA2" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unlock your skin's natural glow overnight with this curated collection designed to soothe and hydrate while you sleep. Apply these essential treatments in </t>
+        </is>
+      </c>
+      <c r="AB2" s="12" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care &gt; Facial Skin Care</t>
+        </is>
+      </c>
+      <c r="AC2" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>morning-brightness-routine</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Morning Brightness Routine | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;Morning Brightness Routine&lt;/strong&gt; by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Mariobadescu (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu Morning Brightness Routine Skincare Kit</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Start your day with a luminous complexion using this energizing routine tailored to brighten and revitalize tired skin. These high-performance formulas work together to defend against daily environmental stressors while providing an instant, healthy-looking glow.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Formulated to brighten dull skin and improve clarity.&lt;/li&gt;&lt;li&gt;Provides essential daytime antioxidant protection.&lt;/li&gt;&lt;li&gt;Lightweight textures absorb quickly for effortless layering.&lt;/li&gt;&lt;li&gt;Boosts skin radiance for a fresh and energized appearance.&lt;/li&gt;&lt;li&gt;Ideal for creating a smooth canvas for makeup application.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;Includes: Brightening cleanser, serum, and daytime moisturizer. Compatibility: Suitable for daily morning use for all skin types.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Mariobadescu</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care &gt; Facial Skin Care</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care &gt; Facial Skin Care</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Skincare Set, Morning Routine, Brightening, Vitamin C, All Skin Types, Daily Care</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>MORNING-BRIGHTNESS-R-FIXED</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>115.00</t>
         </is>
       </c>
-      <c r="R3" s="11" t="inlineStr"/>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr"/>
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="11" t="inlineStr">
+      <c r="T3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U3" s="11" t="inlineStr"/>
-      <c r="V3" s="11" t="inlineStr">
+      <c r="U3" s="12" t="inlineStr"/>
+      <c r="V3" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0618/8476/0291/files/1-MorningBrighteningBundle_OnWhite.jpg?v=1792518688</t>
         </is>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X3" s="11" t="inlineStr">
-        <is>
-          <t>Morning Brightness Routine - Mariobadescu Official Product View</t>
-        </is>
-      </c>
-      <c r="Y3" s="11" t="inlineStr">
+      <c r="X3" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu Morning Brightness Routine collection featuring daily brightening skincare products on a white background.</t>
+        </is>
+      </c>
+      <c r="Y3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z3" s="11" t="inlineStr">
-        <is>
-          <t>Morning Brightness Routine | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="AA3" s="11" t="inlineStr">
-        <is>
-          <t>The  Morning Brightness Routine  by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineere</t>
-        </is>
-      </c>
-      <c r="AB3" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC3" s="11" t="inlineStr">
+      <c r="Z3" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu Morning Brightness Routine Skincare Kit</t>
+        </is>
+      </c>
+      <c r="AA3" s="12" t="inlineStr">
+        <is>
+          <t>Start your day with a luminous complexion using this energizing routine tailored to brighten and revitalize tired skin. These high-performance formulas wor</t>
+        </is>
+      </c>
+      <c r="AB3" s="12" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care &gt; Facial Skin Care</t>
+        </is>
+      </c>
+      <c r="AC3" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>complete-pdrn-routine</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Complete PDRN Routine | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;Complete PDRN Routine&lt;/strong&gt; by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Mariobadescu (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu Complete PDRN Routine Skin Set</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Transform your complexion with the regenerative power of our advanced PDRN routine designed to strengthen and revitalize skin elasticity. Use this system consistently to support a firm, youthful appearance and improve the overall resilience of your skin barrier.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Utilizes advanced PDRN technology for deep cellular support.&lt;/li&gt;&lt;li&gt;Visibly improves skin firmness and overall elasticity.&lt;/li&gt;&lt;li&gt;Helps reinforce the natural moisture barrier against damage.&lt;/li&gt;&lt;li&gt;Smoothes the appearance of fine lines and uneven texture.&lt;/li&gt;&lt;li&gt;Advanced formula suitable for all skin types and ages.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;Includes: PDRN-infused serum and restorative cream. Compatibility: Daily use for firming and anti-aging benefits.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Mariobadescu</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care &gt; Facial Skin Care</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care &gt; Facial Skin Care</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>PDRN, Anti-Aging, Firming, Skincare Routine, Mario Badescu, Skin Barrier</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>COMPLETE-PDRN-ROUTIN-FIXED</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="Q4" s="12" t="inlineStr">
         <is>
           <t>76.00</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr"/>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="R4" s="12" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="T4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr">
+      <c r="U4" s="12" t="inlineStr"/>
+      <c r="V4" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0618/8476/0291/files/On-White_4000x4000_PDRN-Bundle.jpg?v=1788283131</t>
         </is>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X4" s="11" t="inlineStr">
-        <is>
-          <t>Complete PDRN Routine - Mariobadescu Official Product View</t>
-        </is>
-      </c>
-      <c r="Y4" s="11" t="inlineStr">
+      <c r="X4" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu Complete PDRN Routine set featuring regenerative facial skincare products on a white background.</t>
+        </is>
+      </c>
+      <c r="Y4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
-        <is>
-          <t>Complete PDRN Routine | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="AA4" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The  Complete PDRN Routine  by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to </t>
-        </is>
-      </c>
-      <c r="AB4" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC4" s="11" t="inlineStr">
+      <c r="Z4" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu Complete PDRN Routine Skin Set</t>
+        </is>
+      </c>
+      <c r="AA4" s="12" t="inlineStr">
+        <is>
+          <t>Transform your complexion with the regenerative power of our advanced PDRN routine designed to strengthen and revitalize skin elasticity. Use this system c</t>
+        </is>
+      </c>
+      <c r="AB4" s="12" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care &gt; Facial Skin Care</t>
+        </is>
+      </c>
+      <c r="AC4" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>salon-gift-certificates</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Salon Gift Certificates | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;Salon Gift Certificates&lt;/strong&gt; by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Mariobadescu (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu Salon Physical Gift Certificate</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Treat someone special to the ultimate relaxation experience with a physical gift certificate redeemable at our iconic Mario Badescu salon. This elegant gift is the perfect way to provide a loved one with world-class facial treatments and expert skincare services.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Redeemable for professional services at the Mario Badescu Salon.&lt;/li&gt;&lt;li&gt;Physical card shipped directly to your preferred address.&lt;/li&gt;&lt;li&gt;The perfect gift for any skincare enthusiast or fan.&lt;/li&gt;&lt;li&gt;High-quality presentation for a premium gifting experience.&lt;/li&gt;&lt;li&gt;Flexible usage for a variety of salon treatments.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;Type: Physical Gift Certificate. Redemption: Valid for in-salon services only.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Mariobadescu</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Business &amp; Industrial &gt; Customer Service &gt; Gift Certificates</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Business &amp; Industrial &gt; Customer Service &gt; Gift Certificates</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Gift Card, Salon Services, Gift Ideas, Mario Badescu Salon, Physical Gift</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>SALON-GIFT-CERTIFICA-FIXED</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="12" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="R5" s="12" t="inlineStr"/>
+      <c r="S5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T5" s="11" t="inlineStr">
+      <c r="T5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U5" s="11" t="inlineStr"/>
-      <c r="V5" s="11" t="inlineStr">
+      <c r="U5" s="12" t="inlineStr"/>
+      <c r="V5" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0618/8476/0291/files/Salon_Gfit_Certificate.jpg?v=1735236303</t>
         </is>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X5" s="11" t="inlineStr">
-        <is>
-          <t>Salon Gift Certificates - Mariobadescu Official Product View</t>
-        </is>
-      </c>
-      <c r="Y5" s="11" t="inlineStr">
+      <c r="X5" s="12" t="inlineStr">
+        <is>
+          <t>Physical Mario Badescu Salon gift certificate card on a clean white background.</t>
+        </is>
+      </c>
+      <c r="Y5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z5" s="11" t="inlineStr">
-        <is>
-          <t>Salon Gift Certificates | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="AA5" s="11" t="inlineStr">
-        <is>
-          <t>The  Salon Gift Certificates  by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered t</t>
-        </is>
-      </c>
-      <c r="AB5" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC5" s="11" t="inlineStr">
+      <c r="Z5" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu Salon Physical Gift Certificate</t>
+        </is>
+      </c>
+      <c r="AA5" s="12" t="inlineStr">
+        <is>
+          <t>Treat someone special to the ultimate relaxation experience with a physical gift certificate redeemable at our iconic Mario Badescu salon. This elegant gif</t>
+        </is>
+      </c>
+      <c r="AB5" s="12" t="inlineStr">
+        <is>
+          <t>Business &amp; Industrial &gt; Customer Service &gt; Gift Certificates</t>
+        </is>
+      </c>
+      <c r="AC5" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>custom-gift-certificate</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Custom Gift Certificate | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;Custom Gift Certificate&lt;/strong&gt; by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Mariobadescu (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu E-Gift Certificate</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Give the gift of personalized skincare with a convenient e-gift certificate that allows recipients to choose their favorite Mario Badescu products. Delivered instantly via email, this flexible option is ideal for last-minute gifting and ensures your loved one gets exactly what they need.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Delivered via email for instant, hassle-free gifting.&lt;/li&gt;&lt;li&gt;Redeemable for any product across the Mario Badescu online store.&lt;/li&gt;&lt;li&gt;Allows recipients to curate their own personalized skincare routine.&lt;/li&gt;&lt;li&gt;The perfect solution for birthdays, holidays, and special occasions.&lt;/li&gt;&lt;li&gt;No expiration dates for maximum shopping convenience.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;Type: Digital E-Gift Card. Redemption: Valid for online store purchases only.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Mariobadescu</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Business &amp; Industrial &gt; Customer Service &gt; Gift Certificates</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Business &amp; Industrial &gt; Customer Service &gt; Gift Certificates</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>E-Gift Card, Digital Gift, Skincare Gift, Online Shopping, Mario Badescu</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>CUSTOM-GIFT-CERTIFIC-FIXED</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T6" s="11" t="inlineStr">
+      <c r="T6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U6" s="11" t="inlineStr"/>
-      <c r="V6" s="11" t="inlineStr">
+      <c r="U6" s="12" t="inlineStr"/>
+      <c r="V6" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0618/8476/0291/products/0010229_e-card-service.jpg?v=1685100092</t>
         </is>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X6" s="11" t="inlineStr">
-        <is>
-          <t>Custom Gift Certificate - Mariobadescu Official Product View</t>
-        </is>
-      </c>
-      <c r="Y6" s="11" t="inlineStr">
+      <c r="X6" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu digital e-gift certificate card design displayed on screen.</t>
+        </is>
+      </c>
+      <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z6" s="11" t="inlineStr">
-        <is>
-          <t>Custom Gift Certificate | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="AA6" s="11" t="inlineStr">
-        <is>
-          <t>The  Custom Gift Certificate  by Mariobadescu represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered t</t>
-        </is>
-      </c>
-      <c r="AB6" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC6" s="11" t="inlineStr">
+      <c r="Z6" s="12" t="inlineStr">
+        <is>
+          <t>Mario Badescu E-Gift Certificate</t>
+        </is>
+      </c>
+      <c r="AA6" s="12" t="inlineStr">
+        <is>
+          <t>Give the gift of personalized skincare with a convenient e-gift certificate that allows recipients to choose their favorite Mario Badescu products. Deliver</t>
+        </is>
+      </c>
+      <c r="AB6" s="12" t="inlineStr">
+        <is>
+          <t>Business &amp; Industrial &gt; Customer Service &gt; Gift Certificates</t>
+        </is>
+      </c>
+      <c r="AC6" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
